--- a/reports/Debug-purgatory-20260105/Week Total (Prior Year)_Revenue.xlsx
+++ b/reports/Debug-purgatory-20260105/Week Total (Prior Year)_Revenue.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="64">
   <si>
     <t>DepartmentTitle</t>
   </si>
@@ -106,22 +106,16 @@
     <t>account</t>
   </si>
   <si>
+    <t>T101</t>
+  </si>
+  <si>
     <t>T110</t>
   </si>
   <si>
-    <t>T101</t>
-  </si>
-  <si>
-    <t>T103</t>
-  </si>
-  <si>
-    <t>T104</t>
+    <t>T105</t>
   </si>
   <si>
     <t>T100</t>
-  </si>
-  <si>
-    <t>T105</t>
   </si>
   <si>
     <t>department</t>
@@ -574,7 +568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26.7109375" customWidth="1"/>
@@ -591,18 +585,24 @@
         <v>29</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="D2" s="2">
-        <v>894.00</v>
+        <v>4224.30</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -610,10 +610,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D3" s="2">
         <v>510.00</v>
@@ -624,13 +624,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D4" s="2">
-        <v>478461.19</v>
+        <v>348.00</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -638,378 +638,336 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D5" s="2">
-        <v>2385.00</v>
+        <v>325949.10</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>33</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="B6" s="2"/>
       <c r="C6" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D6" s="2">
-        <v>24.75</v>
+        <v>126157.95</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>34</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="B7" s="2"/>
       <c r="C7" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D7" s="2">
-        <v>687143.48</v>
+        <v>3784.00</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>35</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D8" s="2">
-        <v>348.00</v>
+        <v>131238.08</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D9" s="2">
-        <v>153155.28</v>
+        <v>17037.88</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D10" s="2">
-        <v>3784.00</v>
+        <v>65571.26</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D11" s="2">
-        <v>172997.08</v>
+        <v>12177.70</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D12" s="2">
-        <v>23887.72</v>
+        <v>18675.71</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D13" s="2">
-        <v>75578.29</v>
+        <v>24527.62</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D14" s="2">
-        <v>13391.59</v>
+        <v>47408.21</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" s="2">
-        <v>21355.43</v>
+        <v>5508.59</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D16" s="2">
-        <v>35658.44</v>
+        <v>1200.00</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D17" s="2">
-        <v>52609.65</v>
+        <v>27582.45</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D18" s="2">
-        <v>6043.44</v>
+        <v>84142.10</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D19" s="2">
-        <v>1500.00</v>
+        <v>12699.92</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D20" s="2">
-        <v>31210.27</v>
+        <v>1060.00</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D21" s="2">
-        <v>97356.03</v>
+        <v>292245.28</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D22" s="2">
-        <v>14566.30</v>
+        <v>20111.00</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D23" s="2">
-        <v>1060.00</v>
+        <v>4381.65</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D24" s="2">
-        <v>333911.99</v>
+        <v>10733.38</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D25" s="2">
-        <v>20111.00</v>
+        <v>1350.00</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D26" s="2">
-        <v>4381.65</v>
+        <v>1476.72</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D27" s="2">
-        <v>10733.38</v>
+        <v>4657.87</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D28" s="2">
-        <v>1350.00</v>
+        <v>2849.32</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D29" s="2">
-        <v>1476.72</v>
+        <v>2226.52</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D30" s="2">
-        <v>4657.87</v>
+        <v>4057.54</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D31" s="2">
-        <v>3297.54</v>
+        <v>97055.81</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D32" s="2">
-        <v>4267.82</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D33" s="2">
-        <v>4057.54</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D34" s="2">
-        <v>124864.52</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D35" s="2">
         <v>750.00</v>
       </c>
     </row>
